--- a/data/trans_orig/IP16B98-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16B98-Edad-trans_orig.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>40,54%</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17006</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32418</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38513</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>44211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
